--- a/content/Question Bank/MCQ/Python/Unit 13 - Debugging/Unit 13 - Debugging - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 13 - Debugging/Unit 13 - Debugging - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 13" sheetId="1" r:id="Rf9c64b32c626455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 13" sheetId="1" r:id="R46c265c5c7b949cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -405,15 +405,17 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="18" customHeight="1">
+    <x:row r="2" ht="60" hidden="0" customHeight="1">
       <x:c r="A2" s="1" t="str">
         <x:v>Python - MCQ - 13.1.1</x:v>
       </x:c>
       <x:c r="B2" s="1" t="str">
-        <x:v>A developer's code throws an error intermittently, so they wrap it in a broad try/except that silently ignores the exception and moves on, without ever finding the cause. Why does the debugging mindset discourage this?</x:v>
+        <x:v>Preserve evidence before attempting a repair
+A delivery-fee calculator sometimes produces a negative total. A teammate proposes changing three formulas until the symptom disappears.
+Which response creates the strongest starting point for investigation?</x:v>
       </x:c>
       <x:c r="C2" s="2" t="str">
-        <x:v>Hiding a bug without understanding its cause does not make it go away; an unexplained bug typically resurfaces later, often in a worse or harder-to-trace form, whereas understanding the root cause prevents that recurrence.</x:v>
+        <x:v>Debugging begins with a reproducible discrepancy and a testable hypothesis. Several simultaneous edits destroy evidence about which cause mattered.</x:v>
       </x:c>
       <x:c r="D2" s="4" t="n">
         <x:v>1</x:v>
@@ -422,10 +424,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G2" s="2" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H2" s="1" t="str">
         <x:v>python - Set 1</x:v>
@@ -441,41 +443,35 @@
       </x:c>
       <x:c r="L2" s="1"/>
       <x:c r="M2" s="1" t="str">
-        <x:v>Broad try/except blocks cannot handle intermittent errors</x:v>
+        <x:v>Replace all three formulas and retain whichever result looks reasonable.</x:v>
       </x:c>
       <x:c r="N2" s="1" t="str">
-        <x:v>Silently ignoring exceptions always improves performance</x:v>
+        <x:v>Document one failing case and a testable cause hypothesis.</x:v>
       </x:c>
       <x:c r="O2" s="1" t="str">
-        <x:v>It does not matter, since the error message is gone</x:v>
+        <x:v>Add a fallback that converts every negative total to zero.</x:v>
       </x:c>
       <x:c r="P2" s="1" t="str">
-        <x:v>The root cause remains and can trigger the failure again</x:v>
+        <x:v>Rewrite the calculator without first reproducing the behaviour.</x:v>
       </x:c>
       <x:c r="Q2" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="18" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="108" hidden="0" customHeight="1">
       <x:c r="A3" s="1" t="str">
         <x:v>Python - MCQ - 13.1.2</x:v>
       </x:c>
       <x:c r="B3" s="1" t="str">
-        <x:v>A data-import bug is being traced across two functions.
+        <x:v>Keep a required validation active
+A ticket site uses the following check at its public input boundary. The rule must still be enforced when Python runs with optimization enabled.
 ```python
-def load_counts(raw_counts):
-    print(f"loaded: {raw_counts!r}")
-    return raw_counts
-def total_rsvps(raw_counts):
-    counts = load_counts(raw_counts)
-    print(f"about to sum: {counts!r}")
-    return sum(counts)
-total_rsvps([2, 3, "1"])
+assert requested_seats &gt; 0, "seat count must be positive"
 ```
-Both prints show the bad "1" already present. What does this tell you?</x:v>
+Which replacement is most appropriate?</x:v>
       </x:c>
       <x:c r="C3" s="2" t="str">
-        <x:v>Since the bad value appears unchanged at every printed step, the problem is not introduced inside `load_counts` or `total_rsvps`; it must already exist in whatever code built the original list before either function ran.</x:v>
+        <x:v>Explicit validation always runs. An assertion is unsuitable as the only enforcement mechanism because optimized execution can remove it.</x:v>
       </x:c>
       <x:c r="D3" s="4" t="n">
         <x:v>1</x:v>
@@ -487,7 +483,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G3" s="2" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H3" s="1" t="str">
         <x:v>python - Set 1</x:v>
@@ -499,39 +495,42 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K3" s="1" t="str">
-        <x:v>debugging-techniques</x:v>
+        <x:v>assertions</x:v>
       </x:c>
       <x:c r="L3" s="1"/>
       <x:c r="M3" s="1" t="str">
-        <x:v>The bug is inside `total_rsvps`, specifically in the `sum()` call</x:v>
+        <x:v>`assert bool(requested_seats)`</x:v>
       </x:c>
       <x:c r="N3" s="1" t="str">
-        <x:v>There is no bug, since both prints ran successfully</x:v>
+        <x:v>`print("invalid") if requested_seats &lt;= 0 else None`</x:v>
       </x:c>
       <x:c r="O3" s="1" t="str">
-        <x:v>The return statement in `load_counts` created the bad value</x:v>
+        <x:v>Convert the value with `abs()`, store it, and continue without reporting that the submitted input was invalid.</x:v>
       </x:c>
       <x:c r="P3" s="1" t="str">
-        <x:v>The bad value was created before either function ran</x:v>
+        <x:v>`if requested_seats &lt;= 0: raise ValueError("seat count must be positive")`</x:v>
       </x:c>
       <x:c r="Q3" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A4" t="str">
         <x:v>Python - MCQ - 13.1.3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>A registration form uses an assertion for user input.
-```python
-age_text = input("Enter your age: ")
-assert age_text.isdigit(), "must be digits"
-```
-Why is this considered a misuse of assert?</x:v>
+        <x:v>Locate the first state corruption while stepping
+A debugger pauses before each loop update. The developer records these states:
+| Iteration | `price` before update | `total` before update | `total` after update |
+|---:|---:|---:|---:|
+| 1 | `20` | `0` | `20` |
+| 2 | `15` | `20` | `35` |
+| 3 | `8` | `35` | `280` |
+The intended update is addition.
+Which conclusion is best supported by the trace?</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>assert is meant for catching bugs in your own logic that should be logically impossible, not for validating ordinary, expected bad input from a user; using assert here crashes the whole program on normal bad input that should instead be handled gracefully with if/raise or try/except.</x:v>
+        <x:v>The first two additions are correct. The value first diverges when the third update changes `35` to `280`, focusing inspection on that iteration's statement.</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:v>1</x:v>
@@ -540,10 +539,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H4" t="str">
         <x:v>python - Set 1</x:v>
@@ -555,34 +554,40 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>assertions</x:v>
+        <x:v>python-debugger</x:v>
       </x:c>
       <x:c r="L4"/>
       <x:c r="M4" t="str">
-        <x:v>assert always passes no matter what the input value is</x:v>
+        <x:v>Inspect iteration three; its update is the first divergence.</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>assert cannot be used to check string methods like `isdigit()`</x:v>
+        <x:v>The first price is corrupt because it is larger than the third price.</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>Expected bad input needs explicit validation, not `assert`</x:v>
+        <x:v>The second iteration must have changed `price` from an integer to text.</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>Assertions are automatically removed during every Python run</x:v>
+        <x:v>The final value proves that the input collection contains exactly 280 items.</x:v>
       </x:c>
       <x:c r="Q4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A5" t="str">
         <x:v>Python - MCQ - 13.1.4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>A developer is reviewing a teammate's code that relies on assert statements to catch logic errors during testing. What happens when an assert statement's condition evaluates to `False`?</x:v>
+        <x:v>Complete a logging configuration for useful evidence
+An unattended import job should store warnings and more severe events in `import.log`. Existing calls such as `logging.warning(...)` must not be rewritten.
+```python
+import logging
+logging.basicConfig(______________________________)
+```
+Which completion meets both requirements?</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>If an assert's condition is false, Python immediately raises an `AssertionError` at that exact line, optionally with the message provided after the comma; if the condition is true, nothing happens and execution simply continues.</x:v>
+        <x:v>`filename` selects the file destination, while `WARNING` keeps warnings, errors, and critical records eligible.</x:v>
       </x:c>
       <x:c r="D5" t="n">
         <x:v>1</x:v>
@@ -591,10 +596,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G5" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H5" t="str">
         <x:v>python - Set 1</x:v>
@@ -606,34 +611,42 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>assertions</x:v>
+        <x:v>logging</x:v>
       </x:c>
       <x:c r="L5"/>
       <x:c r="M5" t="str">
-        <x:v>The condition is ignored and execution continues</x:v>
+        <x:v>`level=logging.DEBUG`</x:v>
       </x:c>
       <x:c r="N5" t="str">
-        <x:v>Python raises `AssertionError` at that line</x:v>
+        <x:v>`format="import.log"`</x:v>
       </x:c>
       <x:c r="O5" t="str">
-        <x:v>Python prints a warning but continues running normally</x:v>
+        <x:v>`filename="import.log", level=logging.WARNING`</x:v>
       </x:c>
       <x:c r="P5" t="str">
-        <x:v>The program pauses and waits for user input</x:v>
+        <x:v>`message="WARNING", destination="import.log", enabled=True`</x:v>
       </x:c>
       <x:c r="Q5" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A6" t="str">
         <x:v>Python - MCQ - 13.1.5</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>A teammate is stuck mid-bugfix on a chat app: a message queue sometimes drops the last entry, and she wants to pause the script at the exact line where messages are appended so she can inspect variables interactively. Which function, when called inside your code, pauses execution at that exact line and drops you into an interactive (Pdb) prompt?</x:v>
+        <x:v>Keep the smallest case that still carries the defect
+A report fails while summing values loaded from a large CSV. These reductions are tried:
+```python
+sum([4, "6", 2])   # fails
+sum([4, "6"])      # fails
+sum(["6"])         # fails
+sum([6])            # succeeds
+```
+Which case is the best minimal reproduction of the same mixed-type summation defect?</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>Python's built-in `breakpoint()` function, called anywhere in your code, pauses execution at that exact line and hands control to an interactive debugger prompt, letting you inspect any variable available at that point.</x:v>
+        <x:v>The single string still reproduces the same `sum` type failure. Replacing it with integer `6` crosses the boundary into a successful case.</x:v>
       </x:c>
       <x:c r="D6" t="n">
         <x:v>1</x:v>
@@ -642,10 +655,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H6" t="str">
         <x:v>python - Set 1</x:v>
@@ -657,47 +670,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>debugging-workflow</x:v>
       </x:c>
       <x:c r="L6"/>
       <x:c r="M6" t="str">
-        <x:v>`debug()` function</x:v>
+        <x:v>`sum([6])`, because successful code is easier to inspect</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>`pause()` function</x:v>
+        <x:v>`sum(["6"])`, the smallest shown case that still fails</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>`breakpoint()`</x:v>
+        <x:v>The entire CSV, because removing any row changes the program</x:v>
       </x:c>
       <x:c r="P6" t="str">
-        <x:v>`stop()` function</x:v>
+        <x:v>An empty list, because it has the fewest possible elements</x:v>
       </x:c>
       <x:c r="Q6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="66" hidden="0" customHeight="1">
       <x:c r="A7" t="str">
         <x:v>Python - MCQ - 13.1.6</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>A debugger is paused just before an accumulator update.
-```
-&gt; tracker.py(4)total_rsvps()
--&gt; total += attendee.rsvp_count
-(Pdb) total
-0
-(Pdb) attendee.rsvp_count
-2
-(Pdb) n
-&gt; tracker.py(3)total_rsvps()
--&gt; for attendee in attendees:
-(Pdb) total
-```
-What value does pdb report for total on the second check?</x:v>
+        <x:v>Treat an AI repair as a hypothesis
+An AI assistant suggests returning `0` whenever a billing calculation raises an exception. The original requirement says invalid records must be reported, not silently converted into free orders.
+Which next action is responsible?</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>Typing n ran the line total += `attendee.rsvp_count`, which added the current attendee's `rsvp_count` of 2 to the previous total of 0, so the second check correctly reports total as 2.</x:v>
+        <x:v>The proposal conflicts with the stated contract. An AI suggestion is a hypothesis that must be understood and tested against requirements.</x:v>
       </x:c>
       <x:c r="D7" t="n">
         <x:v>1</x:v>
@@ -706,10 +708,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G7" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H7" t="str">
         <x:v>python - Set 1</x:v>
@@ -721,34 +723,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>ai-assisted-debugging</x:v>
       </x:c>
       <x:c r="L7"/>
       <x:c r="M7" t="str">
-        <x:v>0, unchanged since nothing happened</x:v>
+        <x:v>Accept the change because the traceback disappears.</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>An error, because total was never defined</x:v>
+        <x:v>Apply it only in production, where failures matter most.</x:v>
       </x:c>
       <x:c r="O7" t="str">
-        <x:v>2, because the addition line ran</x:v>
+        <x:v>Keep it if the generated explanation sounds confident.</x:v>
       </x:c>
       <x:c r="P7" t="str">
-        <x:v>`None`, because pdb reports only object references</x:v>
+        <x:v>Reject it if tests show that it hides invalid data.</x:v>
       </x:c>
       <x:c r="Q7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="66" hidden="0" customHeight="1">
       <x:c r="A8" t="str">
         <x:v>Python - MCQ - 13.1.7</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>A developer setting up logging for a new fitness-tracking app needs to choose the right severity level for each message, from routine step-count updates to a failed database write. What are Python's five standard logging levels, listed from least to most severe?</x:v>
+        <x:v>Choose a probe that exposes invisible data
+A discount lookup contains the key `"VIP"`, but a value read from a file appears as `VIP` on screen and fails the lookup. Hidden whitespace and type confusion are both plausible.
+Which temporary probe tests both theories in one observation?</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>The logging module defines five standard levels in increasing order of severity: DEBUG, INFO, WARNING, ERROR, and CRITICAL, and choosing the right level for each message is the entire point of using logging instead of plain print statements.</x:v>
+        <x:v>`!r` reveals quotes and hidden whitespace, and the type name distinguishes text from other value types.</x:v>
       </x:c>
       <x:c r="D8" t="n">
         <x:v>1</x:v>
@@ -757,10 +761,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F8" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G8" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H8" t="str">
         <x:v>python - Set 1</x:v>
@@ -772,34 +776,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>logging</x:v>
+        <x:v>debugging-techniques</x:v>
       </x:c>
       <x:c r="L8"/>
       <x:c r="M8" t="str">
-        <x:v>ERROR, CRITICAL, WARNING, INFO, DEBUG</x:v>
+        <x:v>`print(f"code={code!r}, type={type(code).__name__}")`</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>CRITICAL, ERROR, WARNING, INFO, DEBUG</x:v>
+        <x:v>`print("code")`</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>INFO, DEBUG, ERROR, WARNING, CRITICAL</x:v>
+        <x:v>`print(code == code)`</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>DEBUG, INFO, WARNING, ERROR, CRITICAL</x:v>
+        <x:v>`print(len("VIP"))` and assume the incoming value has the same length</x:v>
       </x:c>
       <x:c r="Q8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="66" hidden="0" customHeight="1">
       <x:c r="A9" t="str">
         <x:v>Python - MCQ - 13.1.8</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>A program shipped to production has `basicConfig(level=logging.DEBUG)` still set, flooding the real log file with fine-grained debug detail meant only for development. What is the simplest fix, and why does logging make this easy?</x:v>
+        <x:v>Stop immediately before the suspicious call
+A total becomes wrong somewhere inside `apply_discounts(order)`. The developer wants to inspect `order` just before that function starts and then step into it.
+Where should `breakpoint()` be placed?</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Changing the single level setting to something like WARNING or INFO silences the debug and possibly info messages without touching any of the individual `logging.debug()` or `logging.info()` calls scattered through the code, which is exactly the selective quieting plain `print()` statements cannot offer.</x:v>
+        <x:v>Pausing immediately before the call exposes the caller's argument state and permits the developer to step into the suspected function.</x:v>
       </x:c>
       <x:c r="D9" t="n">
         <x:v>1</x:v>
@@ -808,10 +814,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G9" t="str">
-        <x:v>analyze</x:v>
+        <x:v>understand</x:v>
       </x:c>
       <x:c r="H9" t="str">
         <x:v>python - Set 1</x:v>
@@ -823,34 +829,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>logging</x:v>
+        <x:v>python-debugger</x:v>
       </x:c>
       <x:c r="L9"/>
       <x:c r="M9" t="str">
-        <x:v>Logging cannot be filtered once a program is running</x:v>
+        <x:v>At the end of the program, after the total is displayed</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Raise the configured level; keep the existing log calls</x:v>
+        <x:v>Inside an unrelated input helper that already works</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Every `logging.debug()` call must be deleted by hand</x:v>
+        <x:v>Immediately before the call to `apply_discounts(order)`</x:v>
       </x:c>
       <x:c r="P9" t="str">
-        <x:v>The only fix is to replace all logging calls with `print()`</x:v>
+        <x:v>After deleting the call to `apply_discounts(order)`</x:v>
       </x:c>
       <x:c r="Q9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="66" hidden="0" customHeight="1">
       <x:c r="A10" t="str">
         <x:v>Python - MCQ - 13.1.9</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>A developer is debugging a large, multi-file program and wants to isolate the bug efficiently rather than searching everywhere at once. What is the first recommended step when isolating a minimal failing case?</x:v>
+        <x:v>Determine which records survive a logging threshold
+A service is configured with `level=logging.WARNING`. During one request it issues messages at `INFO`, `ERROR`, `WARNING`, and `DEBUG`, in that order.
+Which sequence remains eligible for the configured handler?</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>The first move is confirming the bug does not actually require the full program, like file reading or command-line arguments, by reproducing it outside the full program using only the specific data and function involved.</x:v>
+        <x:v>With a `WARNING` threshold, `DEBUG` and `INFO` are filtered out; `WARNING` and `ERROR` remain eligible in their issue order.</x:v>
       </x:c>
       <x:c r="D10" t="n">
         <x:v>1</x:v>
@@ -859,10 +867,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F10" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H10" t="str">
         <x:v>python - Set 1</x:v>
@@ -874,34 +882,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>debugging-workflow</x:v>
+        <x:v>logging</x:v>
       </x:c>
       <x:c r="L10"/>
       <x:c r="M10" t="str">
-        <x:v>Reproduce the same bug with only essential code and data</x:v>
+        <x:v>`INFO`, `ERROR`, `WARNING`, `DEBUG`</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Delete the entire project completely and start over from scratch</x:v>
+        <x:v>`ERROR`, `WARNING`</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Immediately ask an AI assistant without trying anything first</x:v>
+        <x:v>`INFO`, `DEBUG`</x:v>
       </x:c>
       <x:c r="P10" t="str">
-        <x:v>Add print statements to every function in every file</x:v>
+        <x:v>`WARNING` only</x:v>
       </x:c>
       <x:c r="Q10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="66" hidden="0" customHeight="1">
       <x:c r="A11" t="str">
         <x:v>Python - MCQ - 13.1.10</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>An AI assistant suggests a fix for a bug. According to responsible AI-assisted debugging, what must happen before trusting and using that fix?</x:v>
+        <x:v>Turn a vague failure into an answerable request
+A developer needs help with an intermittent stock-count defect. Four possible messages are prepared.
+Which message gives another developer the strongest basis for investigation?</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>The fix deserves the same scrutiny as code you wrote yourself: read and understand it to confirm it actually addresses the diagnosed cause, then rerun your own minimal failing case to verify the original error is genuinely gone, since a plausible-looking fix can still address the wrong problem.</x:v>
+        <x:v>The evidence package lets a helper reproduce the mismatch and evaluate a concrete explanation instead of guessing from a vague symptom.</x:v>
       </x:c>
       <x:c r="D11" t="n">
         <x:v>1</x:v>
@@ -913,7 +923,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H11" t="str">
         <x:v>python - Set 1</x:v>
@@ -925,34 +935,44 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>ai-assisted-debugging</x:v>
+        <x:v>debugging-workflow</x:v>
       </x:c>
       <x:c r="L11"/>
       <x:c r="M11" t="str">
-        <x:v>Understand it, then rerun the original failing case</x:v>
+        <x:v>“Inventory is broken; please rewrite it.”</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Paste it immediately because generated fixes are already verified</x:v>
+        <x:v>A screenshot of the editor without the failing input or reproduction steps</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Reject all AI suggestions automatically without ever reading them at all</x:v>
+        <x:v>The entire repository followed only by “any ideas?”</x:v>
       </x:c>
       <x:c r="P11" t="str">
-        <x:v>Ask a second AI assistant to verify the first one's answer instead of testing it yourself</x:v>
+        <x:v>The minimal case, exact mismatch, evidence, and current hypothesis</x:v>
       </x:c>
       <x:c r="Q11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A12" t="str">
         <x:v>Python - MCQ - 13.2.1</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>What is the correct mindset to hold when a program crashes with a traceback?</x:v>
+        <x:v>Trace the final value after a silent logic defect
+A loyalty system is expected to add points for every purchase. A temporary trace is added to the current implementation.
+```python
+points = 10
+for purchase in [5, 8, 3]:
+    if purchase &gt;= 5:
+        points += purchase
+    else:
+        points = purchase
+```
+What final value should the trace record for `points`?</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>A crash is information about a specific gap between what you expected and what actually happened, not a judgment on your skill as a programmer; treating it that way keeps you focused on the gap instead of on self-doubt.</x:v>
+        <x:v>The updates produce `15`, then `23`, then the `else` branch replaces the accumulated value with `3`.</x:v>
       </x:c>
       <x:c r="D12" t="n">
         <x:v>1</x:v>
@@ -961,10 +981,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F12" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H12" t="str">
         <x:v>python - Set 2</x:v>
@@ -980,30 +1000,38 @@
       </x:c>
       <x:c r="L12"/>
       <x:c r="M12" t="str">
-        <x:v>It means you are simply not cut out for programming</x:v>
+        <x:v>`3`</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>It means the Python interpreter has been permanently damaged</x:v>
+        <x:v>`26`</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>It should be ignored and the program rerun until it works</x:v>
+        <x:v>`18`</x:v>
       </x:c>
       <x:c r="P12" t="str">
-        <x:v>Treat it as useful evidence about an expectation mismatch</x:v>
+        <x:v>`13`</x:v>
       </x:c>
       <x:c r="Q12" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A13" t="str">
         <x:v>Python - MCQ - 13.2.2</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>A device's grading script throws a traceback moments before a submission deadline, and panic sets in as red error text fills the terminal. A senior helps calmly, and the device wonders whether they could ever get that good. According to the debugging mindset, what kind of skill is debugging?</x:v>
+        <x:v>Prevent a diagnostic branch from being shadowed
+A temperature monitor is intended to log a critical message at 100°C or above and a warning from 80°C upward.
+```python
+if temperature &gt;= 80:
+    logging.warning("high")
+elif temperature &gt;= 100:
+    logging.critical("shutdown")
+```
+Which smallest repair makes the critical branch reachable while preserving the two thresholds?</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>Debugging is a learnable procedure: form a clear idea of what the code should do, observe what it actually does, and systematically narrow the gap between the two, rather than an innate talent some people simply have.</x:v>
+        <x:v>The broader `&gt;= 80` condition currently captures every value that also meets `&gt;= 100`. Testing the more specific threshold first makes both branches reachable.</x:v>
       </x:c>
       <x:c r="D13" t="n">
         <x:v>1</x:v>
@@ -1015,7 +1043,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>python - Set 2</x:v>
@@ -1027,34 +1055,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>debugging-techniques</x:v>
+        <x:v>logging</x:v>
       </x:c>
       <x:c r="L13"/>
       <x:c r="M13" t="str">
-        <x:v>Something that can only be done by rereading code silently</x:v>
+        <x:v>Change `elif` to a second independent `if`.</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>A process that only senior developers can perform well</x:v>
+        <x:v>Change the warning threshold from 80 to 100.</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>A learnable process for comparing expected and actual behavior</x:v>
+        <x:v>Check `&gt;= 100` first, then use `elif` for `&gt;= 80`.</x:v>
       </x:c>
       <x:c r="P13" t="str">
-        <x:v>A fixed personality trait that some people are born with</x:v>
+        <x:v>Delete the critical branch and log every case as a warning.</x:v>
       </x:c>
       <x:c r="Q13" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="66" hidden="0" customHeight="1">
       <x:c r="A14" t="str">
         <x:v>Python - MCQ - 13.2.3</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>A new intern on a shopping cart project watches the team lead sprinkle temporary output statements through the code while chasing a bug, and asks what this technique is. What is print debugging?</x:v>
+        <x:v>Distinguish an internal invariant from user validation
+A function receives a user-entered quantity and later calculates a warehouse balance that, according to verified program logic, can never be negative.
+Which design uses assertions and validation in their intended roles?</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Print debugging means placing deliberate, temporary `print()` calls around suspicious lines to observe a value's actual state at each step, narrowing a vague bug into a precise, specific mismatch between expected and actual values.</x:v>
+        <x:v>External input requires explicit validation, while an assertion appropriately documents an internal state that correct program logic promises.</x:v>
       </x:c>
       <x:c r="D14" t="n">
         <x:v>1</x:v>
@@ -1063,10 +1093,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F14" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>python - Set 2</x:v>
@@ -1078,34 +1108,41 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>debugging-techniques</x:v>
+        <x:v>assertions</x:v>
       </x:c>
       <x:c r="L14"/>
       <x:c r="M14" t="str">
-        <x:v>Printing only the final output of a program at the very end</x:v>
+        <x:v>Validate user input explicitly; assert the internal balance invariant.</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>A Python function that locates and fixes bugs automatically</x:v>
+        <x:v>Assert the user's quantity and silently clamp a negative internal balance.</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Printing the entire source code of a program out to a separate file</x:v>
+        <x:v>Use assertions for both checks because both values are numeric.</x:v>
       </x:c>
       <x:c r="P14" t="str">
-        <x:v>Temporary print calls that reveal state during execution</x:v>
+        <x:v>Use neither check because later failures will reveal invalid states.</x:v>
       </x:c>
       <x:c r="Q14" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A15" t="str">
         <x:v>Python - MCQ - 13.2.4</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>While fixing a bug in a to-do list app, a developer inserts temporary print statements around suspicious lines. The bug turns out to be buried deep inside nested function calls that run hundreds of times per second, flooding the terminal. What does this situation show about print debugging?</x:v>
+        <x:v>Select an input that exposes an off-by-one defect
+A function should accept percentages from 0 through 100 inclusive, but its guard is:
+```python
+if percent &gt; 0 and percent &lt; 100:
+    return "accepted"
+return "rejected"
+```
+Which test set most directly exposes both incorrect boundaries?</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>Print debugging works well for a specific, localized suspicion but does not scale well to deeply nested logic, since rerunning and re-reading scattered prints across multiple files is slow and easy to lose track of; an interactive debugger is better suited here.</x:v>
+        <x:v>The specification includes both endpoints, but the strict comparisons reject exactly `0` and `100`.</x:v>
       </x:c>
       <x:c r="D15" t="n">
         <x:v>1</x:v>
@@ -1114,10 +1151,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F15" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G15" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>python - Set 2</x:v>
@@ -1129,34 +1166,42 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>debugging-workflow</x:v>
       </x:c>
       <x:c r="L15"/>
       <x:c r="M15" t="str">
-        <x:v>Print debugging scales best because it shows every iteration</x:v>
+        <x:v>`1` and `99`</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Print debugging is always the best tool regardless of bug depth</x:v>
+        <x:v>`-1` and `101`</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>It scales poorly; pdb can inspect the nested state directly</x:v>
+        <x:v>`50` and `75`</x:v>
       </x:c>
       <x:c r="P15" t="str">
-        <x:v>The bug cannot be found without rewriting the entire program</x:v>
+        <x:v>`0` and `100`</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A16" t="str">
         <x:v>Python - MCQ - 13.2.5</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>A developer's program crashes, and they immediately start changing random lines and rerunning, hoping something works. What is the main problem with this approach?</x:v>
+        <x:v>Compare two probes that appear equivalent
+A parser may receive either integer `7` or string `"7"`. Two developers propose these probes:
+```python
+# Probe 1
+print(value)
+# Probe 2
+print(repr(value), type(value).__name__)
+```
+Why is Probe 2 more useful for this investigation?</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Randomly changing code without forming a specific theory about the cause is the most common unproductive response to an error, and it usually takes longer than calmly reading the traceback and testing one clear hypothesis at a time.</x:v>
+        <x:v>Plain display can make integer `7` and string `"7"` look alike. Representation plus type exposes the distinction without changing the value.</x:v>
       </x:c>
       <x:c r="D16" t="n">
         <x:v>1</x:v>
@@ -1168,7 +1213,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H16" t="str">
         <x:v>python - Set 2</x:v>
@@ -1184,35 +1229,40 @@
       </x:c>
       <x:c r="L16"/>
       <x:c r="M16" t="str">
-        <x:v>It is the fastest way to fix any bug</x:v>
+        <x:v>It automatically converts text into an integer.</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Python refuses to run after three failed attempts</x:v>
+        <x:v>It reveals representation and type hidden by Probe 1.</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>It is inefficient only when the program has many files</x:v>
+        <x:v>It prevents the parser from raising any exception.</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>It tests no specific theory, so changes become guesswork</x:v>
+        <x:v>It permanently records the observation in a log file.</x:v>
       </x:c>
       <x:c r="Q16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="198" hidden="0" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>Python - MCQ - 13.2.6</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>A team-splitting helper is under review.
+        <x:v>Find the condition under which two versions diverge
+Two repairs are proposed for a value that may be `None`, `0`, or a positive integer.
 ```python
-def split_into_teams(attendees, team_size):
-    return len(attendees) // team_size
+# Version A
+if value is None:
+    value = 10
+# Version B
+if not value:
+    value = 10
 ```
-Why is predicting that `team_size=0` will break this function, before ever running it, a sign of good debugging mindset?</x:v>
+Which statement is correct?</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Anticipating which inputs would break a function, here a `team_size` of 0 causing a `ZeroDivisionError`, shows the habit of asking 'what input would break this' proactively, which is exactly the calm, structured questioning this mindset is meant to build.</x:v>
+        <x:v>`0` is falsy but is not `None`. Version B replaces a valid zero, whereas Version A preserves it.</x:v>
       </x:c>
       <x:c r="D17" t="n">
         <x:v>1</x:v>
@@ -1224,7 +1274,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H17" t="str">
         <x:v>python - Set 2</x:v>
@@ -1236,40 +1286,40 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>debugging-techniques</x:v>
+        <x:v>debugging-workflow</x:v>
       </x:c>
       <x:c r="L17"/>
       <x:c r="M17" t="str">
-        <x:v>It proactively tests an assumption with a likely failure case</x:v>
+        <x:v>They are equivalent for every Python value.</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>It proves the function is unusable for every possible input</x:v>
+        <x:v>They differ only when `value` is a negative integer.</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>It means the entire function should simply be deleted</x:v>
+        <x:v>At `0`, only Version B replaces the value.</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>It has no real value since Python catches all such errors automatically</x:v>
+        <x:v>They are not equivalent when `value` is `None`; only Version A replaces it.</x:v>
       </x:c>
       <x:c r="Q17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="132" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>Python - MCQ - 13.2.7</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>A parser may receive text with hidden whitespace.
+        <x:v>Complete an assertion that checks the whole invariant
+Earlier application logic guarantees that a computed probability must stay within the closed interval from 0 to 1.
 ```python
-value = "3 "
-print(f"Value: {value}")
-print(f"Value: {value!r}")
+probability = calculate_probability(data)
+assert ____________________, "probability outside [0, 1]"
 ```
-Why does the second print line catch bugs the first one would miss?</x:v>
+Which condition checks precisely that invariant?</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>Using !r prints the value's `repr()`, the precise unambiguous form, which reveals subtle differences like a trailing space, an empty string versus `None`, or '3' versus 3 that a plain f-string display would render identically and hide.</x:v>
+        <x:v>The chained comparison includes both endpoints and rejects every value below 0 or above 1.</x:v>
       </x:c>
       <x:c r="D18" t="n">
         <x:v>1</x:v>
@@ -1278,10 +1328,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F18" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G18" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H18" t="str">
         <x:v>python - Set 2</x:v>
@@ -1293,34 +1343,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>debugging-techniques</x:v>
+        <x:v>assertions</x:v>
       </x:c>
       <x:c r="L18"/>
       <x:c r="M18" t="str">
-        <x:v>`!r` makes the program execute faster</x:v>
+        <x:v>`0 &lt;= probability &lt;= 1`</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>`repr()` exposes details such as the trailing space</x:v>
+        <x:v>`probability`</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>!r converts the value into an integer before it is ever printed</x:v>
+        <x:v>`probability &gt; 0 or probability &lt; 1`</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>!r is required syntax and has no effect on the displayed text</x:v>
+        <x:v>`type(probability) is str`</x:v>
       </x:c>
       <x:c r="Q18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="66" hidden="0" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>Python - MCQ - 13.2.8</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>Why should debug `print()` statements added temporarily during investigation be removed or commented out once the bug is fixed?</x:v>
+        <x:v>Choose the least intrusive tool for a one-run state transition
+A short script fails only once, and the developer needs to compare one variable immediately before and after a single assignment. Interactive stepping and durable production records are unnecessary.
+Which approach is most proportionate?</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Leftover debug prints clutter the real program output and confuse anyone reading it later, including your future self, so once they have served their purpose of finding the bug they should be removed or clearly commented out.</x:v>
+        <x:v>Two temporary, labelled probes answer the narrow before-and-after question with less machinery than a debugger or durable logging setup.</x:v>
       </x:c>
       <x:c r="D19" t="n">
         <x:v>1</x:v>
@@ -1332,7 +1384,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G19" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H19" t="str">
         <x:v>python - Set 2</x:v>
@@ -1344,34 +1396,42 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>debugging-techniques</x:v>
+        <x:v>python-debugger</x:v>
       </x:c>
       <x:c r="L19"/>
       <x:c r="M19" t="str">
-        <x:v>They clutter real output and confuse future readers</x:v>
+        <x:v>Configure rotating log files for the whole application.</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>Python automatically deletes unused print statements</x:v>
+        <x:v>Rewrite the assignment as a separate class.</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>They make the program run out of memory over time</x:v>
+        <x:v>Add a permanent breakpoint to the released program.</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>Leaving them in always causes a `SyntaxError`</x:v>
+        <x:v>Use labelled prints on both sides of the assignment.</x:v>
       </x:c>
       <x:c r="Q19" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A20" t="str">
         <x:v>Python - MCQ - 13.2.9</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>A developer uses assert to check that a bank withdrawal never overdraws the account, planning to rely on that check even in production. Why is assert risky for a check that must always run, and what should be used instead?</x:v>
+        <x:v>Reconstruct execution from ordered log records
+An order processor records:
+```text
+INFO validate order=41
+INFO reserve stock order=41
+ERROR payment declined order=41
+```
+No “dispatch created” record follows.
+Which conclusion is supported without guessing beyond the evidence?</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Python can run with assertions stripped out entirely using the -O optimization flag, so any check that must always run for correctness, like rejecting an overdraft, needs a real if/raise rather than relying on assert, which is only a development-time sanity check.</x:v>
+        <x:v>The ordered records establish validation, reservation, and payment failure. They do not prove why dispatch is absent beyond the missing observation.</x:v>
       </x:c>
       <x:c r="D20" t="n">
         <x:v>1</x:v>
@@ -1380,10 +1440,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F20" t="str">
-        <x:v>hard</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G20" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H20" t="str">
         <x:v>python - Set 2</x:v>
@@ -1395,34 +1455,42 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>assertions</x:v>
+        <x:v>logging</x:v>
       </x:c>
       <x:c r="L20"/>
       <x:c r="M20" t="str">
-        <x:v>assert cannot compare numbers, only strings</x:v>
+        <x:v>Validation failed before stock reservation.</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>There is no practical difference between `assert` and `if`/`raise`</x:v>
+        <x:v>Payment followed reservation; no dispatch record follows.</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Assertions may be disabled with `-O`; use `if`/`raise`</x:v>
+        <x:v>Dispatch definitely ran but logging hid it.</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>if/raise is slower and only used for style reasons</x:v>
+        <x:v>Payment succeeded because the order had already reserved stock.</x:v>
       </x:c>
       <x:c r="Q20" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A21" t="str">
         <x:v>Python - MCQ - 13.2.10</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>A developer suspects a bug occurs only when a specific attendee's `rsvp_count` is negative, inside a loop processing many attendees. What is the most effective use of `breakpoint()` here?</x:v>
+        <x:v>Repair a probe that changes program behaviour
+A developer tries to inspect the next item of an iterator:
+```python
+items = iter([10, 20, 30])
+print("next:", next(items))
+process(items)
+```
+The diagnostic consumes `10`, so `process` begins at `20`.
+Which smallest repair observes the data without consuming the iterator passed to `process`?</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Placing `breakpoint()` inside the loop body lets the developer pause on every iteration and inspect each attendee's `rsvp_count` directly, or combine it with a conditional check so the pause only triggers when the suspicious condition is actually met, rather than guessing from outside the loop.</x:v>
+        <x:v>Calling `next` is a mutation of iterator state. Materializing once allows observation while preserving all elements for a fresh iterator.</x:v>
       </x:c>
       <x:c r="D21" t="n">
         <x:v>1</x:v>
@@ -1446,42 +1514,42 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>debugging-techniques</x:v>
       </x:c>
       <x:c r="L21"/>
       <x:c r="M21" t="str">
-        <x:v>`breakpoint()` can only ever be placed before the loop begins, never inside it at all</x:v>
+        <x:v>Call `next(items)` twice so the effect is consistent.</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Call `breakpoint()` once before the loop and let it detect negatives automatically</x:v>
+        <x:v>Move the same `next(items)` call below `process(items)`.</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>There is no way at all to inspect any loop variables using pdb here</x:v>
+        <x:v>Materialize once; inspect and process the complete collection.</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>Place `breakpoint()` inside `if attendee.rsvp_count &lt; 0` in the loop</x:v>
+        <x:v>Catch `StopIteration` and continue with the shortened iterator.</x:v>
       </x:c>
       <x:c r="Q21" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A22" t="str">
         <x:v>Python - MCQ - 13.3.1</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>An event summary function is tested with no attendees.
-```python
-def average_rsvps(attendees):
-    assert len(attendees) &gt; 0, "attendees list must not be empty"
-    total = sum(a.rsvp_count for a in attendees)
-    return total / len(attendees)
-average_rsvps([])
+        <x:v>Diagnose a nested-call failure from stack evidence
+The debugger shows this call chain:
+```text
+build_report(records)
+  -&gt; total_cost(records)
+       -&gt; normalize(record["cost"])
 ```
-What happens when this runs?</x:v>
+It is paused inside `normalize`, where `value == "12 USD"`. The caller `total_cost` supplied that value unchanged.
+Which hypothesis best fits the observed frames?</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Since the attendees list is empty, `len(attendees)` &gt; 0 is `False`, so Python immediately raises `AssertionError`: attendees list must not be empty at that line, rather than letting execution continue to a less informative `ZeroDivisionError` two lines later.</x:v>
+        <x:v>The live frame proves malformed text entered `normalize` from its caller. It does not establish facts about later rendering or every other record.</x:v>
       </x:c>
       <x:c r="D22" t="n">
         <x:v>1</x:v>
@@ -1490,10 +1558,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H22" t="str">
         <x:v>python - Set 3</x:v>
@@ -1505,42 +1573,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>assertions</x:v>
+        <x:v>python-debugger</x:v>
       </x:c>
       <x:c r="L22"/>
       <x:c r="M22" t="str">
-        <x:v>The assert immediately raises `AssertionError` with its message</x:v>
+        <x:v>The report renderer corrupted the value after `normalize` returned.</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>It returns the value 0 silently with no error at all</x:v>
+        <x:v>Malformed text enters `normalize`; inspect parsing there.</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>It returns `None` because the assertion replaces the return statement</x:v>
+        <x:v>`total_cost` has already produced the correct final report.</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>It raises `ZeroDivisionError` on the total / `len(attendees)` line</x:v>
+        <x:v>The call stack proves every other record has the same malformed value.</x:v>
       </x:c>
       <x:c r="Q22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="66" hidden="0" customHeight="1">
       <x:c r="A23" t="str">
         <x:v>Python - MCQ - 13.3.2</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>An Event class encodes a capacity rule.
-```python
-class Event:
-    def __init__(self, name, max_attendees):
-        assert max_attendees &gt; 0, "an event must allow at least one attendee"
-        self.name = name
-        self.max_attendees = max_attendees
-```
-Beyond catching bugs, what additional value does this assert provide?</x:v>
+        <x:v>Select the smallest repair for a missing diagnostic
+An application contains `logging.info("loaded")`, but nothing appears because no level was configured and the effective threshold is `WARNING`.
+Which smallest change makes the existing informational record eligible?</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>The assert statement makes an assumption about the class explicit and visible to anyone reading the code, documenting directly in the code that a valid Event can never have zero or negative capacity, rather than leaving that rule only in the original author's head.</x:v>
+        <x:v>Lowering the configured threshold to `INFO` makes the existing call eligible without misrepresenting its severity.</x:v>
       </x:c>
       <x:c r="D23" t="n">
         <x:v>1</x:v>
@@ -1552,7 +1614,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H23" t="str">
         <x:v>python - Set 3</x:v>
@@ -1564,39 +1626,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>assertions</x:v>
+        <x:v>logging</x:v>
       </x:c>
       <x:c r="L23"/>
       <x:c r="M23" t="str">
-        <x:v>It replaces the need for the constructor</x:v>
+        <x:v>Replace the call with `logging.critical("loaded")`.</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>It documents the class invariant beside the code</x:v>
+        <x:v>Raise the threshold to `logging.ERROR`.</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>It makes the entire class run measurably faster</x:v>
+        <x:v>Put the call inside `assert logging.info("loaded")`.</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>It allows `max_attendees` to be any negative number safely</x:v>
+        <x:v>Set `basicConfig(level=logging.INFO)` first.</x:v>
       </x:c>
       <x:c r="Q23" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="66" hidden="0" customHeight="1">
       <x:c r="A24" t="str">
         <x:v>Python - MCQ - 13.3.3</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>A developer evaluates a condition while execution is paused.
-```
-(Pdb) p attendee.rsvp_count &gt; 5
-```
-`False`
-What does the `p` command do in this pdb session?</x:v>
+        <x:v>Identify the boundary that makes a reproduction misleading
+A production defect occurs only when duplicate identifiers appear. While reducing the case, a developer removes the duplicate and the program succeeds.
+What should happen next?</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>The p command prints the value of any expression, not just a bare variable name, which is useful for checking something more specific, like a comparison or a computed value, directly at the paused point in execution.</x:v>
+        <x:v>The duplicate is an essential trigger. A minimal failing case must retain the smallest input that continues to produce the target defect.</x:v>
       </x:c>
       <x:c r="D24" t="n">
         <x:v>1</x:v>
@@ -1605,10 +1664,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G24" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H24" t="str">
         <x:v>python - Set 3</x:v>
@@ -1620,41 +1679,42 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>debugging-workflow</x:v>
       </x:c>
       <x:c r="L24"/>
       <x:c r="M24" t="str">
-        <x:v>It permanently changes the value used in the expression</x:v>
+        <x:v>Use the successful case because it contains fewer records.</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>It plots an entire graph of the variable's history</x:v>
+        <x:v>Restore the smallest duplicate pair that still fails.</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>It pauses the entire program permanently, forever</x:v>
+        <x:v>Add unrelated records until some new failure appears.</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>It evaluates and prints an expression in the paused frame</x:v>
+        <x:v>Conclude that duplicate identifiers cannot be involved.</x:v>
       </x:c>
       <x:c r="Q24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A25" t="str">
         <x:v>Python - MCQ - 13.3.4</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>A debugger pauses just before a nested function call.
+        <x:v>Expose a defect in a debugging-only branch
+A diagnostic helper should safely describe any value:
 ```python
-def summarize_event(attendees):
-    breakpoint()
-    total = total_rsvps(attendees)
-    return f"Total RSVPs: {total}"
+def describe(value):
+    if value:
+        return f"value={value!r}"
+    return "length=" + str(len(value))
 ```
-Paused at the `total_rsvps(attendees)` line, what is the key difference between typing n and typing s here?</x:v>
+Which input most directly reveals that the falsy diagnostic branch is itself unsafe?</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>n runs the entire `total_rsvps` call as one step and pauses on the line after it without ever showing what happened inside, while s steps into `total_rsvps` itself, pausing at its very first line so you can follow execution downward into that function.</x:v>
+        <x:v>`None` is falsy but has no length, so the diagnostic branch raises `TypeError`. The other listed inputs take the safe truthy branch.</x:v>
       </x:c>
       <x:c r="D25" t="n">
         <x:v>1</x:v>
@@ -1666,7 +1726,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H25" t="str">
         <x:v>python - Set 3</x:v>
@@ -1678,34 +1738,44 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>debugging-techniques</x:v>
       </x:c>
       <x:c r="L25"/>
       <x:c r="M25" t="str">
-        <x:v>n steps into the function, while s skips over it entirely</x:v>
+        <x:v>`"hello"`</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>`n` steps over the call; `s` steps into it</x:v>
+        <x:v>`[1, 2]`</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>s quits the debugger entirely, while n simply continues it</x:v>
+        <x:v>`None`</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>Both commands run the call and pause on the following line</x:v>
+        <x:v>`"0"`</x:v>
       </x:c>
       <x:c r="Q25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="198" hidden="0" customHeight="1">
       <x:c r="A26" t="str">
         <x:v>Python - MCQ - 13.3.5</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>While chasing a scoring bug in a game leaderboard script, a developer pauses execution in pdb and now wants to move forward one line at a time versus letting the rest of the program run freely. Once paused in pdb, what is the difference between typing n and typing c?</x:v>
+        <x:v>Decide whether moving an assertion preserves behaviour
+Two versions attempt to protect a withdrawal:
+```python
+# Version A
+assert amount &lt;= balance
+balance -= amount
+# Version B
+balance -= amount
+assert balance &gt;= 0
+```
+Assume assertions are enabled and the failed call is caught by a surrounding `try` block. Are the versions equivalent when `amount &gt; balance`?</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>n (next) runs only the current line and pauses again on the following one, letting you step through code one line at a time, while c (continue) resumes normal execution until the next `breakpoint()` call or the program's end.</x:v>
+        <x:v>Version A checks before mutation. Version B subtracts first, so catching its later assertion leaves the negative balance in place.</x:v>
       </x:c>
       <x:c r="D26" t="n">
         <x:v>1</x:v>
@@ -1714,10 +1784,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F26" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H26" t="str">
         <x:v>python - Set 3</x:v>
@@ -1729,34 +1799,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>assertions</x:v>
       </x:c>
       <x:c r="L26"/>
       <x:c r="M26" t="str">
-        <x:v>`n` quits the debugger, while `c` advances one line</x:v>
+        <x:v>No. Version B mutates first; Version A does not.</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>n prints all variables, while c prints only the current one</x:v>
+        <x:v>Yes. Both leave `balance` unchanged whenever the assertion fails.</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>`n` advances one line; `c` resumes to the next stop</x:v>
+        <x:v>Yes. An assertion automatically reverses earlier assignments.</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>n and c do exactly the same identical thing every time</x:v>
+        <x:v>No. Only Version A permits an overdrawn balance to remain.</x:v>
       </x:c>
       <x:c r="Q26" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="66" hidden="0" customHeight="1">
       <x:c r="A27" t="str">
         <x:v>Python - MCQ - 13.3.6</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>After stepping through several lines in pdb and losing track of the surrounding code, which command shows the source code around the current paused line with an arrow marking the exact spot?</x:v>
+        <x:v>Choose a validation workflow for an intermittent failure
+A race-like defect appears about once in fifty runs. A developer changes code after a single successful retry and declares it fixed.
+Which verification strategy gives stronger evidence?</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>The l (list) command prints the source code surrounding the current paused line, with an arrow marking exactly where execution stopped, which is useful for regaining context after several steps.</x:v>
+        <x:v>Repeated trials under captured conditions provide evidence for an intermittent defect, especially when only the suspected factor changes.</x:v>
       </x:c>
       <x:c r="D27" t="n">
         <x:v>1</x:v>
@@ -1765,10 +1837,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F27" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H27" t="str">
         <x:v>python - Set 3</x:v>
@@ -1780,34 +1852,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>debugging-workflow</x:v>
       </x:c>
       <x:c r="L27"/>
       <x:c r="M27" t="str">
-        <x:v>l</x:v>
+        <x:v>Run only the easiest input once after each change.</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>w</x:v>
+        <x:v>Remove timing information so all runs look alike.</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>s</x:v>
+        <x:v>Test several related changes together, then compare only the final outcomes.</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>n</x:v>
+        <x:v>Repeat the captured trigger before and after one focused change.</x:v>
       </x:c>
       <x:c r="Q27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="66" hidden="0" customHeight="1">
       <x:c r="A28" t="str">
         <x:v>Python - MCQ - 13.3.7</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>A developer steps into a function with s, uses u to check that a variable looked correct one level up in the caller, then uses d to come back down. The variable looks wrong only after the inner function runs. What does this narrow down?</x:v>
+        <x:v>Interpret an assertion failure without blaming the assertion
+A sorting function ends with `assert result == sorted(result)`. During testing, that assertion fails.
+Which interpretation is most useful?</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Confirming the variable was correct in the caller before the inner function touched it, but wrong afterward, narrows the bug specifically to logic inside the inner function itself, rather than to bad data arriving from outside it.</x:v>
+        <x:v>The assertion reports that an internal promise was violated. Removing it hides the evidence and does not sort the list.</x:v>
       </x:c>
       <x:c r="D28" t="n">
         <x:v>1</x:v>
@@ -1816,7 +1890,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>hard</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G28" t="str">
         <x:v>analyze</x:v>
@@ -1831,44 +1905,42 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>debugging-techniques</x:v>
+        <x:v>assertions</x:v>
       </x:c>
       <x:c r="L28"/>
       <x:c r="M28" t="str">
-        <x:v>The bug is definitely caused by Python's garbage collector</x:v>
+        <x:v>The assertion has proved that Python's comparison operators are broken.</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>The inner function becomes the strongest suspect</x:v>
+        <x:v>The function violated its sorted-output invariant.</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>The bug must be in the caller instead, not the inner function</x:v>
+        <x:v>Remove the assertion so the returned list becomes sorted.</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>The observations provide no useful clue about the bug's location</x:v>
+        <x:v>Replace the message with a print and assume the output is valid.</x:v>
       </x:c>
       <x:c r="Q28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A29" t="str">
         <x:v>Python - MCQ - 13.3.8</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>A developer asks pdb to show how execution reached the current line.
+        <x:v>Separate operator precedence from the suspected state defect
+A breakpoint shows `ready = False`, `cached = True`, and `admin = False`. The branch uses:
+```python
+if ready or cached and not admin:
+    status = "serve"
+else:
+    status = "wait"
 ```
-(Pdb) w
-  tracker.py(12)&lt;module&gt;()
--&gt; summarize_event(attendees)
-  tracker.py(8)summarize_event()
--&gt; total = total_rsvps(attendees)
-&gt; tracker.py(3)total_rsvps()
--&gt; total += attendee.rsvp_count
-```
-Reading this output bottom to top, what does it represent?</x:v>
+Which result should the developer expect under Python's precedence rules?</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>The w (where) command shows the full call stack, and reading from bottom to top shows the current paused location first, then each function that is waiting for it to finish, one level further out, all the way up to the outermost call.</x:v>
+        <x:v>Python evaluates `not`, then `and`, then `or`. Thus `cached and not admin` is true, making the whole condition true.</x:v>
       </x:c>
       <x:c r="D29" t="n">
         <x:v>1</x:v>
@@ -1880,7 +1952,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H29" t="str">
         <x:v>python - Set 3</x:v>
@@ -1892,34 +1964,41 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>debugging-techniques</x:v>
       </x:c>
       <x:c r="L29"/>
       <x:c r="M29" t="str">
-        <x:v>The current frame and the chain of callers above it</x:v>
+        <x:v>`"wait"`, because `ready` is false.</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>The order in which variables were created over time</x:v>
+        <x:v>`"wait"`, because `or` runs before `and`.</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>The order in which functions are expected to run in the future</x:v>
+        <x:v>`"serve"`, because it evaluates as `ready or (cached and (not admin))`.</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>A list of all functions defined anywhere in the file</x:v>
+        <x:v>A syntax error, because three Boolean operators cannot share a condition.</x:v>
       </x:c>
       <x:c r="Q29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A30" t="str">
         <x:v>Python - MCQ - 13.3.9</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>Paused deep inside `total_rsvps`, a developer wants to check the value of attendees back in `summarize_event` without resuming execution. Which commands accomplish this?</x:v>
+        <x:v>Use truthiness without losing a valid zero
+A sensor function uses `None` for “no reading,” while `0.0` is a valid temperature:
+```python
+if not reading:
+    return "missing"
+return f"{reading:.1f}"
+```
+Which repair preserves the intended distinction?</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>u (up) moves the inspection point one level up the call stack to the caller, `summarize_event`, allowing inspection of its local variables like attendees without resuming, and d (down) moves back down toward the current paused line afterward.</x:v>
+        <x:v>Identity comparison with `None` detects the missing marker without treating the valid falsy reading `0.0` as absent.</x:v>
       </x:c>
       <x:c r="D30" t="n">
         <x:v>1</x:v>
@@ -1928,10 +2007,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H30" t="str">
         <x:v>python - Set 3</x:v>
@@ -1943,34 +2022,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>python-debugger</x:v>
+        <x:v>debugging-workflow</x:v>
       </x:c>
       <x:c r="L30"/>
       <x:c r="M30" t="str">
-        <x:v>s and w</x:v>
+        <x:v>Replace the condition with `if reading is None:`.</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>u and d</x:v>
+        <x:v>Replace it with `if reading == 0:`.</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>n and c</x:v>
+        <x:v>Convert every reading with `bool(reading)` first.</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>p and pp</x:v>
+        <x:v>Return `"missing"` for all non-positive readings.</x:v>
       </x:c>
       <x:c r="Q30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="66" hidden="0" customHeight="1">
       <x:c r="A31" t="str">
         <x:v>Python - MCQ - 13.3.10</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>Why is the call stack, viewable with w, especially useful for a bug buried three or more function calls deep?</x:v>
+        <x:v>Place a breakpoint to distinguish caller and callee theories
+The wrong tax might originate in `prepare_order`, which creates `subtotal`, or in `calculate_tax(subtotal)`. One breakpoint is available for the first run.
+Which placement best separates those theories?</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>When a bug is buried several calls deep, it becomes easy to lose track of who called what; w shows the entire chain of waiting callers at once, letting a developer see the full path execution took to reach the current paused point instead of guessing it.</x:v>
+        <x:v>At the call boundary, the developer can decide whether `prepare_order` supplied a wrong subtotal before investigating tax logic.</x:v>
       </x:c>
       <x:c r="D31" t="n">
         <x:v>1</x:v>
@@ -1982,7 +2063,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G31" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H31" t="str">
         <x:v>python - Set 3</x:v>
@@ -1998,39 +2079,43 @@
       </x:c>
       <x:c r="L31"/>
       <x:c r="M31" t="str">
-        <x:v>It is only useful for single-function programs</x:v>
+        <x:v>After the final receipt is printed</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>It replaces the need to pause execution with a breakpoint</x:v>
+        <x:v>At the start of an unrelated menu loop</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>It shows the caller chain that led to the current frame</x:v>
+        <x:v>Before `prepare_order` has assigned or made `subtotal` available</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>It automatically fixes any bug found in the call chain</x:v>
+        <x:v>Break on the tax call; inspect `subtotal`, then step in</x:v>
       </x:c>
       <x:c r="Q31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="237.60000610351562" hidden="0" customHeight="1">
       <x:c r="A32" t="str">
         <x:v>Python - MCQ - 13.4.1</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>A service configures logging at `WARNING`.
+        <x:v>Trace multiple conditions to find the skipped diagnostic
+A file uploader records one status:
 ```python
-import logging
-logging.basicConfig(level=logging.WARNING)
-logging.debug("detail")
-logging.info("status")
-logging.warning("caution")
-logging.error("failure")
+size = 12
+encrypted = False
+if size &gt; 10:
+    if encrypted:
+        status = "large-secure"
+    else:
+        status = "large-plain"
+else:
+    status = "small"
 ```
-Which messages are actually shown?</x:v>
+Which value should a diagnostic record for `status`?</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>Setting the level to WARNING shows only messages at WARNING severity or higher, so both the debug and info messages are silently skipped while the warning and error messages are shown.</x:v>
+        <x:v>The outer condition is true and the inner condition is false, so the nested `else` assigns `"large-plain"`.</x:v>
       </x:c>
       <x:c r="D32" t="n">
         <x:v>1</x:v>
@@ -2039,10 +2124,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F32" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G32" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H32" t="str">
         <x:v>python - Set 4</x:v>
@@ -2058,30 +2143,38 @@
       </x:c>
       <x:c r="L32"/>
       <x:c r="M32" t="str">
-        <x:v>No messages are shown at all</x:v>
+        <x:v>`"large-secure"`</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>All four messages are shown</x:v>
+        <x:v>`"large-plain"`</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>Only the warning and error messages</x:v>
+        <x:v>`"small"`</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>Only the debug and info messages are shown</x:v>
+        <x:v>`False`</x:v>
       </x:c>
       <x:c r="Q32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A33" t="str">
         <x:v>Python - MCQ - 13.4.2</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>A service fails to open one report file, records the failed operation, and continues serving other requests. Which logging level is most appropriate?</x:v>
+        <x:v>Repair a loop that never reaches its diagnostic exit
+A retry simulation should stop after three failures, but the counter never changes:
+```python
+attempts = 0
+while attempts &lt; 3:
+    logging.warning("retry")
+print("stopped")
+```
+Which smallest repair makes `"stopped"` reachable after exactly three warnings?</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>`logging.error()` (or `logging.critical()` for an unrecoverable, program-ending failure) is appropriate for something that has genuinely failed, as opposed to debug for fine detail, info for routine status, or warning for a recoverable but noteworthy issue.</x:v>
+        <x:v>Incrementing once per iteration changes `attempts` through 1, 2, and 3, after which the loop condition becomes false.</x:v>
       </x:c>
       <x:c r="D33" t="n">
         <x:v>1</x:v>
@@ -2093,7 +2186,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H33" t="str">
         <x:v>python - Set 4</x:v>
@@ -2105,34 +2198,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>logging</x:v>
+        <x:v>debugging-techniques</x:v>
       </x:c>
       <x:c r="L33"/>
       <x:c r="M33" t="str">
-        <x:v>`logging.warning()`</x:v>
+        <x:v>Change the condition to `attempts &lt;= 3`.</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>`logging.error()`</x:v>
+        <x:v>Move `print("stopped")` inside the loop.</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>`logging.debug()`</x:v>
+        <x:v>Add `attempts += 1` after each warning.</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>`logging.info()`</x:v>
+        <x:v>Replace the warning with `logging.critical`.</x:v>
       </x:c>
       <x:c r="Q33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="66" hidden="0" customHeight="1">
       <x:c r="A34" t="str">
         <x:v>Python - MCQ - 13.4.3</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>A developer maintaining a weather-alert app wants to track routine status updates and unusual conditions without cluttering the console the way scattered `print()` calls do. What is the main advantage of `logging.info()` and `logging.warning()` over plain `print()` statements for tracking a program's behavior?</x:v>
+        <x:v>Compare temporary output with durable diagnostics
+A payment service runs unattended and needs timestamps, severity filtering, and file retention. During local investigation, a developer also wants a one-off view of a single variable.
+Which combination best matches the two needs?</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>logging labels each message with its severity automatically, can be silenced by level without touching the code that produces the messages, and can redirect output to a file via `basicConfig(filename=...)`, none of which plain `print()` offers without writing that logic yourself.</x:v>
+        <x:v>Configured logging supports persistent operational evidence; a temporary probe is proportionate for a narrow local observation.</x:v>
       </x:c>
       <x:c r="D34" t="n">
         <x:v>1</x:v>
@@ -2141,10 +2236,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H34" t="str">
         <x:v>python - Set 4</x:v>
@@ -2160,30 +2255,32 @@
       </x:c>
       <x:c r="L34"/>
       <x:c r="M34" t="str">
-        <x:v>Severity labels, level filters, and optional file output</x:v>
+        <x:v>Use logging for service events and a temporary probe locally.</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>`print()` cannot accept f-strings while logging can</x:v>
+        <x:v>Use bare prints for every production event and leave them permanently.</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>`print()` and logging provide the same filtering and severity features</x:v>
+        <x:v>Use assertions as the service's event history and disable logs.</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>logging is only available in Python versions after 3.10</x:v>
+        <x:v>Insert permanent breakpoints wherever a timestamp would be useful.</x:v>
       </x:c>
       <x:c r="Q34" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
+    <x:row r="35" ht="66" hidden="0" customHeight="1">
       <x:c r="A35" t="str">
         <x:v>Python - MCQ - 13.4.4</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>A bug in a large inventory-management system only shows up after processing thousands of records, making it painful to trace through the full program every time. What is the purpose of isolating a minimal failing case when debugging?</x:v>
+        <x:v>Judge a repair against a counterexample
+An AI proposes replacing `if value is None` with `if not value` to handle a missing quantity. The specification allows quantity `0`.
+Which test most efficiently challenges the proposed equivalence?</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Isolating a minimal failing case means stripping away everything not required to trigger a bug, one piece at a time, until a small, self-contained reproduction remains, turning a vague 'something is wrong somewhere' into a specific, answerable question.</x:v>
+        <x:v>Zero is valid but falsy, so it is the smallest counterexample showing that `if not value` changes the intended behaviour.</x:v>
       </x:c>
       <x:c r="D35" t="n">
         <x:v>1</x:v>
@@ -2192,10 +2289,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F35" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H35" t="str">
         <x:v>python - Set 4</x:v>
@@ -2207,34 +2304,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>debugging-workflow</x:v>
+        <x:v>ai-assisted-debugging</x:v>
       </x:c>
       <x:c r="L35"/>
       <x:c r="M35" t="str">
-        <x:v>To make the bug much harder to find on purpose here</x:v>
+        <x:v>`value = 12`</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>Keep removing unrelated code while preserving the failure</x:v>
+        <x:v>`value = "12"`</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>To rewrite the entire program completely from scratch every time</x:v>
+        <x:v>`value = None`</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>To hide the failure from anyone reviewing the code</x:v>
+        <x:v>`value = 0`</x:v>
       </x:c>
       <x:c r="Q35" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="66" hidden="0" customHeight="1">
       <x:c r="A36" t="str">
         <x:v>Python - MCQ - 13.4.5</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>Stuck on a stubborn bug in a chat app's message parser, a developer starts explaining the code out loud line by line to a rubber duck on the desk, and the mistake suddenly becomes obvious. Why does rubber-duck debugging, explaining code out loud sentence by sentence, often surface bugs that silent reading misses?</x:v>
+        <x:v>Determine whether a reduced case still represents the defect
+The full application fails when `int("3 ")` is called after a custom parser deliberately rejects surrounding whitespace. A reduced case calls plain Python `int("3 ")`, which succeeds.
+What does the successful reduction show?</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>Reading code silently lets your eyes skip over a line you already believe is correct, relying on assumptions you already hold, while explaining the same code out loud forces you to state each assumption explicitly, and a wrong assumption sounds noticeably wrong the moment it is spoken.</x:v>
+        <x:v>Plain `int` does not reproduce the custom parser's whitespace policy. Removing that policy removed an essential condition of the defect.</x:v>
       </x:c>
       <x:c r="D36" t="n">
         <x:v>1</x:v>
@@ -2243,10 +2342,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F36" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G36" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H36" t="str">
         <x:v>python - Set 4</x:v>
@@ -2262,30 +2361,32 @@
       </x:c>
       <x:c r="L36"/>
       <x:c r="M36" t="str">
-        <x:v>The physical rubber duck provides hints through careful listening</x:v>
+        <x:v>Python repaired the full application automatically.</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>The duck provides hints based on machine learning models</x:v>
+        <x:v>The reduction removed an essential behaviour.</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Speaking forces hidden assumptions to become explicit</x:v>
+        <x:v>Whitespace can never contribute to a parsing defect.</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>It works by literally compiling the spoken words into code</x:v>
+        <x:v>The original traceback must have named the wrong line.</x:v>
       </x:c>
       <x:c r="Q36" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="66" hidden="0" customHeight="1">
       <x:c r="A37" t="str">
         <x:v>Python - MCQ - 13.4.6</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>A developer has reduced a bug to a function and a class that wraps a single list, and removing the class still reproduces the exact same error message. Should they stop here?</x:v>
+        <x:v>Make a failing assertion identify the relevant record
+A batch check uses `assert total &gt;= 0, "bad total"`. When record 847 fails, the message does not identify the record or value.
+Which revision adds the most useful evidence without changing the invariant?</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>No, the developer should keep removing pieces one at a time and rerunning after each removal; since the class was already shown to be unnecessary, the wrapping class should be dropped and the search should continue with the plain list alone until nothing more can be removed without losing the failure.</x:v>
+        <x:v>The invariant remains `total &gt;= 0`, while the message now identifies both the affected record and its observed value.</x:v>
       </x:c>
       <x:c r="D37" t="n">
         <x:v>1</x:v>
@@ -2294,7 +2395,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F37" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G37" t="str">
         <x:v>analyze</x:v>
@@ -2309,39 +2410,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>debugging-workflow</x:v>
+        <x:v>assertions</x:v>
       </x:c>
       <x:c r="L37"/>
       <x:c r="M37" t="str">
-        <x:v>Yes, any reproduction that crashes is automatically minimal</x:v>
+        <x:v>`assert total, "847"`</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>No. Remove the irrelevant class and keep minimizing</x:v>
+        <x:v>`assert record_id &gt;= 0, f"record={record_id}, total must not be negative"`</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>Yes, because removing more code would change the error message</x:v>
+        <x:v>`assert total &gt;= 0, f"record={record_id}, total={total!r}"`</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>No, minimization should restart from the entire original project</x:v>
+        <x:v>`print("bad total")`</x:v>
       </x:c>
       <x:c r="Q37" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="66" hidden="0" customHeight="1">
       <x:c r="A38" t="str">
         <x:v>Python - MCQ - 13.4.7</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>A reduced test case removes every class from the original program.
-```python
-counts = [2, "3"]
-print(sum(counts))
-```
-This crashes identically to a version using an Attendee class. What does that confirm?</x:v>
+        <x:v>Detect a repair that only moves the failure
+An AI changes a loader so that invalid numeric text becomes `None`. The loader no longer raises, but a later `sum(values)` now fails on `None`.
+Which evaluation is most accurate?</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Since the bug reproduces identically without the Attendee class, the class itself is irrelevant to the bug; the problem is purely about a string ending up inside a list of numbers, narrowing the search away from the class entirely.</x:v>
+        <x:v>The downstream failure shows the loader still violates the expected numeric-data contract; the symptom was relocated, not repaired.</x:v>
       </x:c>
       <x:c r="D38" t="n">
         <x:v>1</x:v>
@@ -2350,10 +2448,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F38" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H38" t="str">
         <x:v>python - Set 4</x:v>
@@ -2365,34 +2463,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>debugging-workflow</x:v>
+        <x:v>ai-assisted-debugging</x:v>
       </x:c>
       <x:c r="L38"/>
       <x:c r="M38" t="str">
-        <x:v>The crash still proves that classes caused the bug</x:v>
+        <x:v>The patch moved the failure downstream without restoring the data contract.</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>The Attendee class is definitely the cause of the bug</x:v>
+        <x:v>The patch is correct because the loader completed successfully.</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>`sum()` cannot ever be used on any list containing numbers</x:v>
+        <x:v>The later exception is unrelated because it occurs in another function.</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>The bug is mixed numeric and string data, not the class</x:v>
+        <x:v>Converting `None` to zero silently is necessarily the intended solution for every invalid record.</x:v>
       </x:c>
       <x:c r="Q38" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="66" hidden="0" customHeight="1">
       <x:c r="A39" t="str">
         <x:v>Python - MCQ - 13.4.8</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>A requirement says inventory must never become negative. Which code most directly turns that invariant into an executable debugging check?</x:v>
+        <x:v>Ask the debugger a question without advancing execution
+Execution is paused before `remaining = capacity - booked`. The developer needs to test the expression `booked &gt; capacity` while keeping the current line unexecuted.
+Which debugger action fits that purpose?</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>An assertion documents and checks the invariant at the point where a negative value would reveal a defect.</x:v>
+        <x:v>`p` evaluates an expression in the paused frame without advancing past the current statement.</x:v>
       </x:c>
       <x:c r="D39" t="n">
         <x:v>1</x:v>
@@ -2404,7 +2504,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H39" t="str">
         <x:v>python - Set 4</x:v>
@@ -2416,34 +2516,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>assertions</x:v>
+        <x:v>python-debugger</x:v>
       </x:c>
       <x:c r="L39"/>
       <x:c r="M39" t="str">
-        <x:v>Add `assert inventory &gt;= 0` after the update</x:v>
+        <x:v>Continue until the program terminates.</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Print `inventory` without checking whether the requirement holds</x:v>
+        <x:v>Step over the assignment and infer the earlier state.</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Convert inventory to a string, which prevents a numeric invariant from being tested</x:v>
+        <x:v>Quit and add an unrelated assertion elsewhere.</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Catch every exception and replace inventory with zero, hiding the operation that caused the defect</x:v>
+        <x:v>Evaluate `booked &gt; capacity` at the prompt with `p`.</x:v>
       </x:c>
       <x:c r="Q39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="66" hidden="0" customHeight="1">
       <x:c r="A40" t="str">
         <x:v>Python - MCQ - 13.4.9</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>Compare adding many temporary `print()` calls with using a breakpoint to inspect a changing state inside a loop. Which approach is better for examining several variables at one exact iteration?</x:v>
+        <x:v>Select the first investigation for unexpected behaviour
+A grade report prints `Pass` for a score that should fail. No exception occurs.
+Which first move gives the investigation a measurable target?</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>A breakpoint pauses at the relevant iteration and supports inspection without scattering temporary output through the code.</x:v>
+        <x:v>Recording the exact expected-versus-actual result for a repeatable input defines the discrepancy that later probes or breakpoints must explain.</x:v>
       </x:c>
       <x:c r="D40" t="n">
         <x:v>1</x:v>
@@ -2452,10 +2554,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F40" t="str">
-        <x:v>hard</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H40" t="str">
         <x:v>python - Set 4</x:v>
@@ -2467,34 +2569,36 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>debugging-techniques</x:v>
+        <x:v>debugging-workflow</x:v>
       </x:c>
       <x:c r="L40"/>
       <x:c r="M40" t="str">
-        <x:v>Use a conditional breakpoint at the target iteration</x:v>
+        <x:v>Capture and reproduce the exact expected-versus-actual result.</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>Add unrelated print calls in every function, producing more output than the defect requires</x:v>
+        <x:v>Catch `Exception` around the entire report and retry without recording the input.</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Change variable names until the bug disappears</x:v>
+        <x:v>Replace the conditional with a random threshold.</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Use neither approach and infer the changing state only from the final screen</x:v>
+        <x:v>Remove the failing student record from the data.</x:v>
       </x:c>
       <x:c r="Q40" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
+    <x:row r="41" ht="66" hidden="0" customHeight="1">
       <x:c r="A41" t="str">
         <x:v>Python - MCQ - 13.4.10</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>A quantity validator should accept every integer from zero upward, but the original code used `quantity &gt; 0`. A teammate changes it to `quantity &gt;= 0` and reports success after testing only `10`. Which verification gives the strongest evidence that the boundary bug is fixed without masking a nearby regression?</x:v>
+        <x:v>Combine evidence, repair, and regression checking
+A booking total is wrong only for discounted group reservations. The team has a reproducible case and an AI-proposed one-line repair.
+Which sequence provides the strongest evidence that the work is complete?</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>The original failing boundary, zero, must pass after the fix. Testing one value on each side as well, 1 and -1, confirms the corrected comparison accepts nearby valid input and still rejects nearby invalid input instead of merely looking plausible.</x:v>
+        <x:v>The sequence ties the repair to observed evidence and checks both the original defect and nearby behaviour for regressions.</x:v>
       </x:c>
       <x:c r="D41" t="n">
         <x:v>1</x:v>
@@ -2503,7 +2607,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F41" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G41" t="str">
         <x:v>analyze</x:v>
@@ -2518,23 +2622,24 @@
         <x:v>debugging</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>debugging-workflow</x:v>
+        <x:v>ai-assisted-debugging</x:v>
       </x:c>
       <x:c r="L41"/>
       <x:c r="M41" t="str">
-        <x:v>Test only `10` again because it is a typical valid value</x:v>
+        <x:v>Apply the line, observe no syntax error, and delete the failing case.</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>Read the changed operator without executing the function</x:v>
+        <x:v>Ask the AI whether its own answer is correct and accept its confidence.</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Replace the validation with a broad exception handler</x:v>
+        <x:v>Trace, explain, and test the patch on original and neighbouring cases.</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Run `0`, `1`, and `-1` to verify both sides of the boundary</x:v>
+        <x:v>Add a broad fallback so every group reservation returns some total.
+---</x:v>
       </x:c>
       <x:c r="Q41" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
